--- a/artfynd/A 12076-2023 artfynd.xlsx
+++ b/artfynd/A 12076-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 12076-2023 artfynd.xlsx
+++ b/artfynd/A 12076-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>110229727</v>
       </c>
       <c r="B2" t="n">
-        <v>56806</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58388</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>339165.1562848273</v>
+        <v>339165</v>
       </c>
       <c r="R2" t="n">
-        <v>6538481.835168079</v>
+        <v>6538482</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -787,37 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>110231094</v>
+        <v>110229730</v>
       </c>
       <c r="B3" t="n">
-        <v>57577</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58388</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208249</v>
+        <v>103001</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>338911.0001534701</v>
+        <v>339292</v>
       </c>
       <c r="R3" t="n">
-        <v>6538330.82483378</v>
+        <v>6538440</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -857,27 +847,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-05-10</t>
+          <t>2023-04-14</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>05:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-05-10</t>
+          <t>2023-04-14</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:10</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ca 2cm</t>
+          <t>05:27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,49 +877,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anna Sjövall</t>
+          <t>Andreas Källman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anna Sjövall</t>
+          <t>Andreas Källman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>110231092</v>
+        <v>110229810</v>
       </c>
       <c r="B4" t="n">
-        <v>57577</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58388</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208249</v>
+        <v>103001</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -944,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>339233.352918188</v>
+        <v>339000</v>
       </c>
       <c r="R4" t="n">
-        <v>6538479.498287289</v>
+        <v>6538404</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,27 +954,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-05-10</t>
+          <t>2023-06-09</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>03:49</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-05-10</t>
+          <t>2023-06-09</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:09</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ca 3cm</t>
+          <t>03:49</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,49 +984,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anna Sjövall</t>
+          <t>Andreas Källman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anna Sjövall</t>
+          <t>Andreas Källman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>110231091</v>
+        <v>110229824</v>
       </c>
       <c r="B5" t="n">
-        <v>57577</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58388</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>208249</v>
+        <v>103001</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1061,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>339011.8200127507</v>
+        <v>339012</v>
       </c>
       <c r="R5" t="n">
-        <v>6538440.22430044</v>
+        <v>6538501</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1096,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>05:45</t>
+          <t>03:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,12 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>05:45</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>5st</t>
+          <t>03:56</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,12 +1091,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anna Sjövall</t>
+          <t>Andreas Källman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anna Sjövall</t>
+          <t>Andreas Källman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1141,12 +1106,7 @@
         <v>110231090</v>
       </c>
       <c r="B6" t="n">
-        <v>57577</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58817</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1187,10 +1147,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>339012.9393623377</v>
+        <v>339013</v>
       </c>
       <c r="R6" t="n">
-        <v>6538442.243269029</v>
+        <v>6538442</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1265,15 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>110231095</v>
+        <v>110231091</v>
       </c>
       <c r="B7" t="n">
-        <v>57577</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58817</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,10 +1260,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>338905.3402801682</v>
+        <v>339012</v>
       </c>
       <c r="R7" t="n">
-        <v>6538331.578537947</v>
+        <v>6538440</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1340,7 +1295,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>05:45</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1350,12 +1305,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>05:45</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Adult</t>
+          <t>5st</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1382,37 +1337,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>110229824</v>
+        <v>110231092</v>
       </c>
       <c r="B8" t="n">
-        <v>56806</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58817</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103001</v>
+        <v>208249</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1422,10 +1372,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>339011.7859222076</v>
+        <v>339233</v>
       </c>
       <c r="R8" t="n">
-        <v>6538501.168010807</v>
+        <v>6538480</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1457,7 +1407,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>03:56</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1467,7 +1417,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>03:56</t>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ca 3cm</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1482,15 +1437,239 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Andreas Källman</t>
+          <t>Anna Sjövall</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Andreas Källman</t>
+          <t>Anna Sjövall</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>110231094</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58817</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Gapungebyn, Dls</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>338911</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6538331</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-05-10</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-05-10</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ca 2cm</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Anna Sjövall</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anna Sjövall</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>110231095</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58817</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Gapungebyn, Dls</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>338905</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6538332</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-05-10</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-05-10</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Adult</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Anna Sjövall</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anna Sjövall</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 12076-2023 artfynd.xlsx
+++ b/artfynd/A 12076-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110229727</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110229730</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110229810</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110229824</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1222,6 +1247,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110231090</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1334,6 +1364,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110231091</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1446,6 +1481,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110231092</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1558,6 +1598,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110231094</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1670,8 +1715,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110231095</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>